--- a/school_surveys/035_self_awareness_questionnaire--school_surveys.xlsx
+++ b/school_surveys/035_self_awareness_questionnaire--school_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -528,7 +528,11 @@
           <t>Introduction</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please take a few minutes to complete this questionnaire to gain a better understanding of your self-awareness levels.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,64 +547,64 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rate_yourself_on_the_scale_of_1_10</t>
+          <t>self_rating</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How would you rate yourself on the scale of 1-10?</t>
+          <t>How would you rate yourself on a scale of 1-10?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>rate_yourself_on_the_scale_of_1_10</t>
+          <t>self_reflection</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rate yourself on the scale of 1-10</t>
+          <t>What do you feel most comfortable with?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>what_do_you_feel_most_comfortable_with</t>
+          <t>major_life_area_of_concern</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What do you feel most comfortable with?</t>
+          <t>What is your major life area of concern?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,12 +616,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>what_do_you_feel_most_uncomfortable_with</t>
+          <t>feelings_about_self</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What do you feel most uncomfortable with?</t>
+          <t>How do you feel about yourself?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +639,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>how_do_you_rate_yourself_on_a_scale_of_1_10</t>
+          <t>rate_your_self</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How do you rate yourself on a scale of 1-10?</t>
+          <t>Rate yourself on a scale of 1-10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +662,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>how_do_you_feel_about_yourself</t>
+          <t>confidence_in_self</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How do you feel about yourself?</t>
+          <t>How confident are you in yourself?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +680,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>rate_your_self_on_a_scale_of_1_to_10</t>
+          <t>self_importance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rate yourself on a scale of 1 to 10</t>
+          <t>What do you feel is your greatest strength?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +708,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>what_is_your_major_life_area_of_concern</t>
+          <t>self_growth</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is your major life area of concern?</t>
+          <t>What areas do you feel you need to improve on?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,366 +726,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rate_your_self_on_a_scale_of_10</t>
+          <t>final_thoughts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rate yourself on a scale of 10</t>
+          <t>Do you have any final thoughts or insights about yourself?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>what_do_you_feel_most_powerful_about_yourself</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>What do you feel most powerful about yourself?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>how_do_you_feel_about_your_self</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>How do you feel about yourself?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>what_do_you_feel_about_your_self</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>What do you feel about yourself?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>rate_your_self_on_a_scale_of_1_to_10</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Rate yourself on a scale of 1 to 10</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>what_do_you_feel_about_your_self</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>What do you feel about yourself?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>how_do_you_feel_about_your_self</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>How do you feel about yourself?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>rate_your_self_on_a_scale_of_1_to_10</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Rate yourself on a scale of 1 to 10</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>how_do_you_feel_about_your_self</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>How do you feel about yourself?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>prophets_1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How do you rate yourself on a scale of 1 to 10?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>prophets_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>How do you feel about yourself?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>prophets_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What do you feel about yourself?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>prophets_4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Rate yourself on a scale of 1 to 10</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>prophets_5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>How do you feel about yourself?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>prophets_6</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What do you feel about yourself?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>prophets_7</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Rate yourself on a scale of 1 to 10</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +757,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
     <col width="39" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +785,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>what_do_you_feel_most_comfortable_with_choices</t>
+          <t>self_reflection_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +802,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>what_do_you_feel_most_comfortable_with_choices</t>
+          <t>self_reflection_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +819,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>what_do_you_feel_most_comfortable_with_choices</t>
+          <t>self_reflection_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,714 +836,306 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>what_do_you_feel_most_uncomfortable_with_choices</t>
+          <t>major_life_area_of_concern_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>my_emotions</t>
+          <t>my_career</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>My emotions</t>
+          <t>My career</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>what_do_you_feel_most_uncomfortable_with_choices</t>
+          <t>major_life_area_of_concern_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>my_thoughts</t>
+          <t>my_relationships</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>My thoughts</t>
+          <t>My relationships</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>what_do_you_feel_most_uncomfortable_with_choices</t>
+          <t>major_life_area_of_concern_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>my_physical_appearance</t>
+          <t>my_health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>My physical appearance</t>
+          <t>My health</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>what_do_you_feel_most_uncomfortable_with_choices</t>
+          <t>major_life_area_of_concern_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>my_personal_growth</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>My personal growth</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>how_do_you_feel_about_yourself_choices</t>
+          <t>feelings_about_self_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>i_am_very_confident</t>
+          <t>i_am_very_happy_with_myself</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>I am very confident</t>
+          <t>I am very happy with myself</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>how_do_you_feel_about_yourself_choices</t>
+          <t>feelings_about_self_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>i_am_somewhat_confident</t>
+          <t>i_am_somewhat_happy_with_myself</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>I am somewhat confident</t>
+          <t>I am somewhat happy with myself</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>how_do_you_feel_about_yourself_choices</t>
+          <t>feelings_about_self_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>i_am_not_very_confident</t>
+          <t>i_am_not_very_happy_with_myself</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>I am not very confident</t>
+          <t>I am not very happy with myself</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>what_is_your_major_life_area_of_concern_choices</t>
+          <t>confidence_in_self_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>my_career</t>
+          <t>i_am_very_confident</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>My career</t>
+          <t>I am very confident</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>what_is_your_major_life_area_of_concern_choices</t>
+          <t>confidence_in_self_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>my_relationships</t>
+          <t>i_am_somewhat_confident</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>My relationships</t>
+          <t>I am somewhat confident</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>what_is_your_major_life_area_of_concern_choices</t>
+          <t>confidence_in_self_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>my_health</t>
+          <t>i_am_not_very_confident</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>My health</t>
+          <t>I am not very confident</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>what_is_your_major_life_area_of_concern_choices</t>
+          <t>self_importance_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>my_personal_growth</t>
+          <t>my_abilities</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>My personal growth</t>
+          <t>My abilities</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>what_do_you_feel_most_powerful_about_yourself_choices</t>
+          <t>self_importance_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>my_abilities</t>
+          <t>my_knowledge</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>My abilities</t>
+          <t>My knowledge</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>what_do_you_feel_most_powerful_about_yourself_choices</t>
+          <t>self_importance_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>my_knowledge</t>
+          <t>my_experiences</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>My knowledge</t>
+          <t>My experiences</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>what_do_you_feel_most_powerful_about_yourself_choices</t>
+          <t>self_importance_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>my_experiences</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>My experiences</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>what_do_you_feel_most_powerful_about_yourself_choices</t>
+          <t>self_growth_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>my_relationships</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>My relationships</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>how_do_you_feel_about_your_self_choices</t>
+          <t>self_growth_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>i_am_very_happy_with_myself</t>
+          <t>my_career</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>I am very happy with myself</t>
+          <t>My career</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>how_do_you_feel_about_your_self_choices</t>
+          <t>self_growth_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>i_am_somewhat_happy_with_myself</t>
+          <t>my_health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>I am somewhat happy with myself</t>
+          <t>My health</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>how_do_you_feel_about_your_self_choices</t>
+          <t>self_growth_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>i_am_not_very_happy_with_myself</t>
+          <t>my_personal_growth</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>I am not very happy with myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>what_do_you_feel_about_your_self_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>i_am_very_proud_of_myself</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>I am very proud of myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>what_do_you_feel_about_your_self_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>i_am_somewhat_proud_of_myself</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>I am somewhat proud of myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>what_do_you_feel_about_your_self_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>i_am_not_very_proud_of_myself</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>I am not very proud of myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>what_do_you_feel_about_your_self_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>i_am_very_confident_in_myself</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>I am very confident in myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>what_do_you_feel_about_your_self_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>i_am_somewhat_confident_in_myself</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>I am somewhat confident in myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>what_do_you_feel_about_your_self_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>i_am_not_very_confident_in_myself</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>I am not very confident in myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>how_do_you_feel_about_your_self_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>i_am_very_happy_with_myself</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>I am very happy with myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>how_do_you_feel_about_your_self_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>i_am_somewhat_happy_with_myself</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>I am somewhat happy with myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>how_do_you_feel_about_your_self_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>i_am_not_very_happy_with_myself</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>I am not very happy with myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>how_do_you_feel_about_your_self_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>i_am_very_confident</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>I am very confident</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>how_do_you_feel_about_your_self_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>i_am_somewhat_confident</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>I am somewhat confident</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>how_do_you_feel_about_your_self_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>i_am_not_very_confident</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>I am not very confident</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>prophets_2_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>i_am_very_happy_with_myself</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>I am very happy with myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>prophets_2_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>i_am_somewhat_happy_with_myself</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>I am somewhat happy with myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>prophets_2_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>i_am_not_very_happy_with_myself</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>I am not very happy with myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>prophets_3_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>i_am_very_confident</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>I am very confident</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>prophets_3_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>i_am_somewhat_confident</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>I am somewhat confident</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>prophets_3_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>i_am_not_very_confident</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>I am not very confident</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>prophets_5_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>i_am_very_happy_with_myself</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>I am very happy with myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>prophets_5_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>i_am_somewhat_happy_with_myself</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>I am somewhat happy with myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>prophets_5_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>i_am_not_very_happy_with_myself</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>I am not very happy with myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>prophets_6_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>i_am_very_confident</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>I am very confident</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>prophets_6_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>i_am_somewhat_confident</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>I am somewhat confident</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>prophets_6_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>i_am_not_very_confident</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>I am not very confident</t>
+          <t>My personal growth</t>
         </is>
       </c>
     </row>
